--- a/ui_runner/templates/graded_analysis_tabs_2026-06-01.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-01.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="G2" t="n">
-        <v>47.4</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>66.7</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
         <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>60.5</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="7">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>167</v>
+        <v>376</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>271</v>
       </c>
       <c r="G8" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="9">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>57.3</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="11">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>624</v>
+        <v>714</v>
       </c>
       <c r="E11" t="n">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F11" t="n">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="G11" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>58.4</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>46.2</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G14" t="n">
-        <v>27.2</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="15">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>374</v>
+        <v>555</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="F15" t="n">
-        <v>302</v>
+        <v>432</v>
       </c>
       <c r="G15" t="n">
-        <v>19.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>137</v>
+        <v>227</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="G16" t="n">
-        <v>11.7</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2579</v>
+        <v>2731</v>
       </c>
       <c r="E17" t="n">
-        <v>613</v>
+        <v>641</v>
       </c>
       <c r="F17" t="n">
-        <v>1966</v>
+        <v>2090</v>
       </c>
       <c r="G17" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
     </row>
   </sheetData>
@@ -1106,73 +1106,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.2</v>
+        <v>58.3</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>17.6</v>
+        <v>33.3</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>28.6</v>
+        <v>38.5</v>
       </c>
       <c r="G2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
       </c>
-      <c r="H2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
       <c r="J2" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="M2" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="P2" t="n">
-        <v>6.2</v>
+        <v>17.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="R2" t="n">
+        <v>45.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="T2" t="n">
+        <v>50</v>
       </c>
       <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>23.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>207</v>
       </c>
       <c r="Z2" t="n">
-        <v>87.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="AA2" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="AB2" t="n">
         <v>100</v>
@@ -1194,52 +1203,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52.2</v>
+        <v>60.7</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>54.1</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>42.9</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="M3" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="N3" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="P3" t="n">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1251,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>16.1</v>
+        <v>21.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="Z3" t="n">
         <v>44</v>
@@ -1372,29 +1381,50 @@
           <t>Below Avg</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>66.7</v>
+      </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>52.9</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="J5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>29.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="N5" t="n">
+        <v>31.8</v>
       </c>
       <c r="O5" t="n">
+        <v>22</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1405,11 +1435,17 @@
       <c r="W5" t="n">
         <v>0</v>
       </c>
+      <c r="X5" t="n">
+        <v>28.6</v>
+      </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>54.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1427,29 +1463,50 @@
           <t>Weak</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>66.7</v>
+      </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="D6" t="n">
+        <v>71</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="F6" t="n">
+        <v>54.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
+      <c r="J6" t="n">
+        <v>66.7</v>
+      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>32.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="P6" t="n">
+        <v>18.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1460,14 +1517,23 @@
       <c r="W6" t="n">
         <v>0</v>
       </c>
+      <c r="X6" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>61.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>50</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1483,94 +1549,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57.3</v>
+        <v>64.7</v>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="D7" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>624</v>
+        <v>714</v>
       </c>
       <c r="F7" t="n">
-        <v>58.4</v>
+        <v>58.9</v>
       </c>
       <c r="G7" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="H7" t="n">
-        <v>46.2</v>
+        <v>46.6</v>
       </c>
       <c r="I7" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J7" t="n">
-        <v>27.2</v>
+        <v>28.6</v>
       </c>
       <c r="K7" t="n">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="L7" t="n">
-        <v>19.3</v>
+        <v>22.2</v>
       </c>
       <c r="M7" t="n">
-        <v>374</v>
+        <v>555</v>
       </c>
       <c r="N7" t="n">
-        <v>11.7</v>
+        <v>15.4</v>
       </c>
       <c r="O7" t="n">
-        <v>137</v>
+        <v>227</v>
       </c>
       <c r="P7" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2579</v>
+        <v>2731</v>
       </c>
       <c r="R7" t="n">
-        <v>47.4</v>
+        <v>46.1</v>
       </c>
       <c r="S7" t="n">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="T7" t="n">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="U7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="V7" t="n">
-        <v>60.5</v>
+        <v>54.8</v>
       </c>
       <c r="W7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="X7" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>376</v>
       </c>
       <c r="Z7" t="n">
-        <v>66.7</v>
+        <v>63.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="AB7" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AD7" t="n">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>

--- a/ui_runner/templates/graded_analysis_tabs_2026-06-01.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-01.xlsx
@@ -474,13 +474,13 @@
         <v>180</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F2" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>46.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="4">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F8" t="n">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="G8" t="n">
-        <v>27.9</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="9">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>64.7</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="11">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>714</v>
+        <v>739</v>
       </c>
       <c r="E11" t="n">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="F11" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="E12" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
-        <v>58.9</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>46.6</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G14" t="n">
-        <v>28.6</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="15">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>555</v>
+        <v>647</v>
       </c>
       <c r="E15" t="n">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="F15" t="n">
-        <v>432</v>
+        <v>487</v>
       </c>
       <c r="G15" t="n">
-        <v>22.2</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="G16" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2731</v>
+        <v>2751</v>
       </c>
       <c r="E17" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F17" t="n">
-        <v>2090</v>
+        <v>2109</v>
       </c>
       <c r="G17" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1154,7 @@
         <v>28</v>
       </c>
       <c r="R2" t="n">
-        <v>45.5</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
         <v>123</v>
@@ -1382,70 +1382,73 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>52.9</v>
+        <v>53.3</v>
       </c>
       <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>33</v>
+      </c>
+      <c r="M5" t="n">
+        <v>91</v>
+      </c>
+      <c r="N5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>40</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="Y5" t="n">
         <v>17</v>
       </c>
-      <c r="F5" t="n">
-        <v>80</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>41</v>
-      </c>
-      <c r="N5" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>22</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>7</v>
-      </c>
       <c r="Z5" t="n">
-        <v>54.5</v>
+        <v>61.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1464,49 +1467,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.7</v>
+        <v>73.2</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>54.5</v>
+        <v>68.8</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>32.9</v>
+        <v>37.2</v>
       </c>
       <c r="M6" t="n">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="N6" t="n">
-        <v>28.6</v>
+        <v>23.8</v>
       </c>
       <c r="O6" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="P6" t="n">
-        <v>18.2</v>
+        <v>12.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1518,16 +1521,16 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>66.7</v>
+        <v>64.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="Z6" t="n">
-        <v>61.5</v>
+        <v>55.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AB6" t="n">
         <v>50</v>
@@ -1549,55 +1552,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64.7</v>
+        <v>66.5</v>
       </c>
       <c r="C7" t="n">
+        <v>167</v>
+      </c>
+      <c r="D7" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>739</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>164</v>
+      </c>
+      <c r="H7" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I7" t="n">
         <v>136</v>
       </c>
-      <c r="D7" t="n">
-        <v>58</v>
-      </c>
-      <c r="E7" t="n">
-        <v>714</v>
-      </c>
-      <c r="F7" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>151</v>
-      </c>
-      <c r="H7" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>133</v>
-      </c>
       <c r="J7" t="n">
-        <v>28.6</v>
+        <v>29.4</v>
       </c>
       <c r="K7" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="L7" t="n">
-        <v>22.2</v>
+        <v>24.7</v>
       </c>
       <c r="M7" t="n">
-        <v>555</v>
+        <v>647</v>
       </c>
       <c r="N7" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="O7" t="n">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="P7" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2731</v>
+        <v>2751</v>
       </c>
       <c r="R7" t="n">
-        <v>46.1</v>
+        <v>47.8</v>
       </c>
       <c r="S7" t="n">
         <v>180</v>
@@ -1615,16 +1618,16 @@
         <v>42</v>
       </c>
       <c r="X7" t="n">
-        <v>27.9</v>
+        <v>29.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="Z7" t="n">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="AB7" t="n">
         <v>52.7</v>
